--- a/ゲーム作成.xlsx
+++ b/ゲーム作成.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\com\source\repos\GameBase\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kazus\source\repos\GameBase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCF4829-6E5C-46CE-BCA7-D7EFDB4CCB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E807AA-3234-4D91-8CBB-78C2E71154BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Player" sheetId="1" r:id="rId1"/>
+    <sheet name="Flow" sheetId="4" r:id="rId1"/>
+    <sheet name="Screen" sheetId="3" r:id="rId2"/>
+    <sheet name="Player" sheetId="1" r:id="rId3"/>
+    <sheet name="Trigger" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="315">
   <si>
     <t>PlayerState</t>
     <phoneticPr fontId="1"/>
@@ -190,10 +190,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>MPcost</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>FireAtk</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -279,10 +275,6 @@
   </si>
   <si>
     <t>Gravity</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Collider</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -389,16 +381,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>当たり判定</t>
-    <rPh sb="0" eb="1">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>向き</t>
     <rPh sb="0" eb="1">
       <t>ム</t>
@@ -412,13 +394,1360 @@
   <si>
     <t>bool</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Valocity</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>double vx, vy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>速度</t>
+    <rPh sb="0" eb="2">
+      <t>ソクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ColliderGround</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ColliderWall</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地面当たり判定</t>
+    <rPh sb="0" eb="2">
+      <t>ジメン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壁の衝突判定</t>
+    <rPh sb="0" eb="1">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウトツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PassivePoint</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>属性耐性はマイナス行くことも考慮して作成</t>
+    <rPh sb="0" eb="2">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイセイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コウリョ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Duration</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クールタイム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詠唱時間</t>
+    <rPh sb="0" eb="2">
+      <t>エイショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マナ消費量</t>
+    <rPh sb="2" eb="4">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>リョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MPCost</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>炎攻撃</t>
+    <rPh sb="0" eb="1">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氷攻撃</t>
+    <rPh sb="0" eb="1">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雷攻撃</t>
+    <rPh sb="0" eb="1">
+      <t>カミナリ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルパワー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>持続時間：バフ</t>
+    <rPh sb="0" eb="4">
+      <t>ジゾクジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>防御力</t>
+    <rPh sb="0" eb="2">
+      <t>ボウギョ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃速度</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>会心率</t>
+    <rPh sb="0" eb="3">
+      <t>カイシンリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>炎耐性増加</t>
+    <rPh sb="0" eb="1">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>タイセイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氷耐性増加</t>
+    <rPh sb="0" eb="1">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>タイセイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雷耐性増加</t>
+    <rPh sb="0" eb="1">
+      <t>カミナリ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>タイセイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基本</t>
+    <rPh sb="0" eb="2">
+      <t>キホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バフ系</t>
+    <rPh sb="2" eb="3">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スピリット補足（名前は未定）</t>
+    <rPh sb="5" eb="7">
+      <t>ホソク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ミテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>獲得方法</t>
+    <rPh sb="0" eb="4">
+      <t>カクトクホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>精霊碑などのオブジェクトを触る</t>
+    <rPh sb="0" eb="2">
+      <t>セイレイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>サワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス撃破報酬</t>
+    <rPh sb="2" eb="6">
+      <t>ゲキハホウシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>装備ルール</t>
+    <rPh sb="0" eb="2">
+      <t>ソウビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大３つ</t>
+    <rPh sb="0" eb="2">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>付け替え可能</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>永続効果</t>
+    <rPh sb="0" eb="4">
+      <t>エイゾクコウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行動やルールそのものを変える永続改造</t>
+    <rPh sb="0" eb="2">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>エイゾク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カイゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>能力例</t>
+    <rPh sb="0" eb="3">
+      <t>ノウリョクレイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステータス常時バフ</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>撃破時に敵を爆発など</t>
+    <rPh sb="0" eb="2">
+      <t>ゲキハ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>バクハツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基本的に入力をしなくていいものとしてスピリットを用意</t>
+    <rPh sb="0" eb="3">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヨウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HP１割以下を確殺</t>
+    <rPh sb="3" eb="4">
+      <t>ワリ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクサツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>補足</t>
+    <rPh sb="0" eb="2">
+      <t>ホソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルとスピリットの違い</t>
+    <rPh sb="10" eb="11">
+      <t>チガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何かしらの入力</t>
+    <rPh sb="0" eb="1">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自動効果</t>
+    <rPh sb="0" eb="2">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>共通で持つものは最小限に</t>
+    <rPh sb="0" eb="2">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>サイショウゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ElementType</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>属性</t>
+    <rPh sb="0" eb="2">
+      <t>ゾクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイコン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>説明</t>
+    <rPh sb="0" eb="2">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルレベル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>std::string?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効果はEffect</t>
+    <rPh sb="0" eb="2">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>StatModifier</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OnKillEffect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OnRollingEffect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RuleOverride</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Spirit</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>炎の守護者</t>
+    <rPh sb="0" eb="1">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>シュゴシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Effects</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Statmodifier</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FireRes+30%</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ATK+10%</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵撃破時に爆破</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="1" eb="4">
+      <t>ゲキハジ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>バクハ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sprit</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>灼熱の魂</t>
+    <rPh sb="0" eb="2">
+      <t>シャクネツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タマシイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OnLillEffect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>explode(radius, fireDmaage)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死神の契約</t>
+    <rPh sb="0" eb="2">
+      <t>シニガミ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ケイヤク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OnHitEffect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>if target.hp &lt; 10% -&gt; instantKill</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル設計：最終ベース上はいったんおいておく</t>
+    <rPh sb="3" eb="5">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ウエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Shadow Roll</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Trigger</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OnRollInput</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Effect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">RuleOverride </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Roll -&gt;Teleport</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CoolDown</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>InputActions</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Move</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動：左右作ってください</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サユウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Roll</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ローリング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Jump</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通常攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bool InputManager::IsPressed(InputAction action)</t>
+  </si>
+  <si>
+    <t>{</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    switch (action)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case InputAction::MoveLeft:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return IsKeyPressed(KeyCode::A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            || IsPadPressed(PadButton::Left);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case InputAction::Jump:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return IsKeyPressed(KeyCode::Space)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            || IsPadPressed(PadButton::A);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return false;</t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t>bool input = InputManager::Instance().IsPressed(InputAction::Jump);</t>
+  </si>
+  <si>
+    <t>if (input) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // ジャンプ処理</t>
+  </si>
+  <si>
+    <t>// 呼び出し</t>
+    <rPh sb="3" eb="4">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bool IsTriggered(InputAction action);   // 押した瞬間</t>
+  </si>
+  <si>
+    <t>bool IsPressed(InputAction action);     // 押している</t>
+  </si>
+  <si>
+    <t>bool IsReleased(InputAction action);    // 離した瞬間</t>
+  </si>
+  <si>
+    <t>enum class SkillSlot : int {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Slot1 = 0,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Slot2,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Slot3,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Slot4,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Slot5,</t>
+  </si>
+  <si>
+    <t>};</t>
+  </si>
+  <si>
+    <t>bool InputManager::IsSkillTriggered(SkillSlot slot)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    switch (slot)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case SkillSlot::Slot1:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return IsKeyTriggered(KeyCode::Num1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            || IsPadTriggered(PadButton::X);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case SkillSlot::Slot2:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return IsKeyTriggered(KeyCode::Num2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            || IsPadTriggered(PadButton::Y);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case SkillSlot::Slot3:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return IsKeyTriggered(KeyCode::Num3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            || IsPadTriggered(PadButton::B);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case SkillSlot::Slot4:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return IsKeyTriggered(KeyCode::Num4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            || IsPadTriggered(PadButton::A);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case SkillSlot::Slot5:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return IsKeyTriggered(KeyCode::Num5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            || IsPadTriggered(PadButton::RB);</t>
+  </si>
+  <si>
+    <t>class Player {</t>
+  </si>
+  <si>
+    <t>private:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::array&lt;std::unique_ptr&lt;Skill&gt;, 5&gt; skills;</t>
+  </si>
+  <si>
+    <t>public:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void Update()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        for (int i = 0; i &lt; skills.size(); ++i)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            if (InputManager::Instance().IsSkillTriggered(</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    static_cast&lt;SkillSlot&gt;(i)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                UseSkill(i);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void UseSkill(int index)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (skills[index])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            skills[index]-&gt;Activate();</t>
+  </si>
+  <si>
+    <t>hp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>exp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>skills</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1~5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dash</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダッシュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最低限動くプレイヤー</t>
+    <rPh sb="0" eb="3">
+      <t>サイテイゲン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TransformComponent</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VelocityComponent</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CollisionComponent</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>x,y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>vx,vy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ground,Wall</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GravitySystem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MovementSystem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CollisionSystem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左右移動</t>
+    <rPh sb="0" eb="2">
+      <t>サユウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地面に立つ</t>
+    <rPh sb="0" eb="2">
+      <t>ジメン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行動</t>
+    <rPh sb="0" eb="2">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>InputSystem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PlayerActionSystem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>InputAction</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Move,Jump,Roll</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追記</t>
+    <rPh sb="0" eb="2">
+      <t>ツイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Triggerはまだ使わない</t>
+    <rPh sb="10" eb="11">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘の最小構成</t>
+    <rPh sb="0" eb="2">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サイショウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AttackComponent</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HitBox</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AttackSystem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HitDetectionSystem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DamageSystem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OnAttack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OnHit</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OnKill</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HP/死亡処理</t>
+    <rPh sb="3" eb="5">
+      <t>シボウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HealthComponent</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DeathSystem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OnDamageTaken</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Onkill</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Trigger-&gt;基盤</t>
+    <rPh sb="9" eb="11">
+      <t>キバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Effectのインターフェイス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Effectの種類</t>
+    <rPh sb="7" eb="9">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>StatModifierEffect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DamageEffect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SpawnEffect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RuleOverrideEffect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EffectSystem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>effectComponent</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル実装</t>
+    <rPh sb="3" eb="5">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Skill + Effect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1Onskill</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2MP消費</t>
+    <rPh sb="3" eb="5">
+      <t>ショウヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3Effect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4CoolDown</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SkillCastSystem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CooldownSystem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ルール変更スキル</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Trigger:OnRoll</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Effect:RuleOverride(Roll -&gt; Teleport)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SpiritComponent</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SpiritSlot</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特徴</t>
+    <rPh sb="0" eb="2">
+      <t>トクチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力無し</t>
+    <rPh sb="0" eb="3">
+      <t>ニュウリョクナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>永続</t>
+    <rPh sb="0" eb="2">
+      <t>エイゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Trigger待ち</t>
+    <rPh sb="7" eb="8">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>爆発</t>
+    <rPh sb="0" eb="2">
+      <t>バクハツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OnLowHP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>即死</t>
+    <rPh sb="0" eb="2">
+      <t>ソクシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常時</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インタラクト/獲得</t>
+    <rPh sb="7" eb="9">
+      <t>カクトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>精霊碑・ボス報酬</t>
+    <rPh sb="0" eb="2">
+      <t>セイレイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホウシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>InteractableComponent</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SpiritGrantComponent</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>InteractionSystem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SpiritEquipSystem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パッシブツリー（余裕がある場合）</t>
+    <rPh sb="8" eb="10">
+      <t>ヨユウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PassiveNodeComponent</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PassiveSystem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>拡張</t>
+    <rPh sb="0" eb="2">
+      <t>カクチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵AI</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス固有Trigger</t>
+    <rPh sb="2" eb="4">
+      <t>コユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>状態異常</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. 移動</t>
+  </si>
+  <si>
+    <t>2. 攻撃</t>
+  </si>
+  <si>
+    <t>3. HP / 死亡</t>
+  </si>
+  <si>
+    <t>4. Trigger → Effect</t>
+  </si>
+  <si>
+    <t>5. スキル</t>
+  </si>
+  <si>
+    <t>6. スピリット</t>
+  </si>
+  <si>
+    <t>7. 獲得手段</t>
+  </si>
+  <si>
+    <t>8. パッシブ</t>
+  </si>
+  <si>
+    <t>実装順</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -428,6 +1757,15 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
@@ -460,11 +1798,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -480,6 +1821,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>572242</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>48121</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0A7AD5A-CB69-D389-6DFD-CE1186F29DC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1428750" y="781050"/>
+          <a:ext cx="5315692" cy="3553321"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -744,383 +2134,1643 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:I31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68D748F9-666A-455C-9C1D-779F202358AC}">
+  <dimension ref="B1:I86"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:9">
+      <c r="I1" t="s">
+        <v>314</v>
+      </c>
+    </row>
     <row r="2" spans="2:9">
-      <c r="B2" t="s">
-        <v>20</v>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>228</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="I2" t="s">
-        <v>38</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>229</v>
+      </c>
+      <c r="D3" t="s">
+        <v>232</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>239</v>
+      </c>
+      <c r="I3" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
       <c r="C4" t="s">
-        <v>1</v>
+        <v>230</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
+        <v>233</v>
+      </c>
+      <c r="F4" t="s">
+        <v>158</v>
+      </c>
+      <c r="I4" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>231</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F5" t="s">
+        <v>240</v>
+      </c>
+      <c r="I5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="I6" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="C7" t="s">
+        <v>235</v>
+      </c>
+      <c r="I7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
+      <c r="C8" t="s">
+        <v>236</v>
+      </c>
+      <c r="I8" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
+      <c r="C9" t="s">
+        <v>237</v>
+      </c>
+      <c r="I9" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="C11" t="s">
+        <v>241</v>
+      </c>
+      <c r="F11" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9">
+      <c r="C12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12" t="s">
+        <v>244</v>
+      </c>
+      <c r="F12" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="C13" t="s">
+        <v>243</v>
+      </c>
+      <c r="D13" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9">
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9">
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9">
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9">
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9">
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9">
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9">
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9">
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
       <c r="C15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>8</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" spans="2:9">
       <c r="C16" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="C17" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="C19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="C20" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="C21" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="C24" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="C25" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="C28" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="C30" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="C31" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33" t="s">
+        <v>146</v>
+      </c>
+      <c r="C33" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="C34" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="C37" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="C38" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3">
+      <c r="C39" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="C40" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3">
+      <c r="C41" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3">
+      <c r="C42" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3">
+      <c r="B44" t="s">
+        <v>146</v>
+      </c>
+      <c r="C44" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3">
+      <c r="C45" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3">
+      <c r="C46" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3">
+      <c r="B48">
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="C49" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="C50" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="C51" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="C52" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="C53" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="C55" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="C56" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="C58" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="C59" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6">
+      <c r="C60" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62">
+        <v>5</v>
+      </c>
+      <c r="C62" t="s">
+        <v>37</v>
+      </c>
+      <c r="F62" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6">
+      <c r="C63" t="s">
+        <v>282</v>
+      </c>
+      <c r="F63" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="C64" t="s">
+        <v>283</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+      <c r="F64" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
+      <c r="F65" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
+      <c r="C66" t="s">
+        <v>261</v>
+      </c>
+      <c r="D66" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6">
+      <c r="C67" t="s">
+        <v>289</v>
+      </c>
+      <c r="D67" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6">
+      <c r="C68" t="s">
+        <v>124</v>
+      </c>
+      <c r="D68" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6">
+      <c r="B70">
+        <v>6</v>
+      </c>
+      <c r="C70" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6">
+      <c r="C71" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6">
+      <c r="C72" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6">
+      <c r="C73" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6">
+      <c r="C74" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6">
+      <c r="C75" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6">
+      <c r="B77">
+        <v>7</v>
+      </c>
+      <c r="C77" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6">
+      <c r="C78" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6">
+      <c r="C79" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3">
+      <c r="B81">
+        <v>8</v>
+      </c>
+      <c r="C81" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3">
+      <c r="C82" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3">
+      <c r="C83" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3">
+      <c r="C84" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3">
+      <c r="C85" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3">
+      <c r="C86" t="s">
+        <v>305</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B3B7205-F7C0-4385-B463-1F4A189C4295}">
+  <dimension ref="B3:I19"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="E19" t="s">
+        <v>223</v>
+      </c>
+      <c r="I19" t="s">
+        <v>224</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:N37"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="1"/>
+    <col min="9" max="9" width="9" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.375" style="1" customWidth="1"/>
+    <col min="12" max="13" width="9" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14">
+      <c r="B2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14">
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14">
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="B5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
+      <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
+      <c r="B13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14">
+      <c r="B14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
+      <c r="B16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
+      <c r="C17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
+      <c r="B18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13">
+      <c r="B19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" t="s">
+      <c r="D20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13">
+      <c r="B21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13">
+      <c r="C22" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13">
+      <c r="C23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13">
+      <c r="B24" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" t="s">
-        <v>63</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" t="s">
+      <c r="C24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13">
+      <c r="F25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13">
+      <c r="B26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13">
+      <c r="B27" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C18" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" t="s">
-        <v>64</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" t="s">
+      <c r="C27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
+      <c r="B28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="B20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7">
-      <c r="C21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7">
-      <c r="B24" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7">
-      <c r="B25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="C28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D28" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="2:7">
-      <c r="B26" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7">
+      <c r="F28" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13">
       <c r="B29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13">
+      <c r="F30" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13">
+      <c r="B31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13">
+      <c r="B32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D32" s="3">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="1" t="s">
+      <c r="F32" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13">
+      <c r="B33" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D33" s="3">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="31" spans="2:7">
-      <c r="B31" s="1" t="s">
+      <c r="F33" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13">
+      <c r="B34" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D34" s="3">
         <v>0.75</v>
       </c>
+      <c r="F34" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13">
+      <c r="B35" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="F35" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13">
+      <c r="G36" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13">
+      <c r="G37" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B35:C35"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F73312A-43C0-4F2C-9A11-0E7EAB938DAA}">
+  <dimension ref="B2:O60"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="12" max="12" width="48.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="47.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:15">
+      <c r="B2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15">
+      <c r="B3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" t="s">
+        <v>154</v>
+      </c>
+      <c r="L3" t="s">
+        <v>161</v>
+      </c>
+      <c r="O3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15">
+      <c r="B4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" t="s">
+        <v>156</v>
+      </c>
+      <c r="L4" t="s">
+        <v>162</v>
+      </c>
+      <c r="O4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15">
+      <c r="B5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" t="s">
+        <v>158</v>
+      </c>
+      <c r="L5" t="s">
+        <v>163</v>
+      </c>
+      <c r="O5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15">
+      <c r="B6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" t="s">
+        <v>160</v>
+      </c>
+      <c r="L6" t="s">
+        <v>164</v>
+      </c>
+      <c r="O6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15">
+      <c r="B7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" t="s">
+        <v>225</v>
+      </c>
+      <c r="L7" t="s">
+        <v>165</v>
+      </c>
+      <c r="O7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="B8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" t="s">
+        <v>227</v>
+      </c>
+      <c r="L8" t="s">
+        <v>166</v>
+      </c>
+      <c r="O8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15">
+      <c r="L9" t="s">
+        <v>167</v>
+      </c>
+      <c r="O9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15">
+      <c r="L11" t="s">
+        <v>168</v>
+      </c>
+      <c r="O11" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15">
+      <c r="L12" t="s">
+        <v>169</v>
+      </c>
+      <c r="O12" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15">
+      <c r="L13" t="s">
+        <v>170</v>
+      </c>
+      <c r="O13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15">
+      <c r="L14" t="s">
+        <v>171</v>
+      </c>
+      <c r="O14" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15">
+      <c r="L15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O15" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15">
+      <c r="L16" t="s">
+        <v>173</v>
+      </c>
+      <c r="O16" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="17" spans="12:15">
+      <c r="L17" t="s">
+        <v>177</v>
+      </c>
+      <c r="O17" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="12:15">
+      <c r="L18" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="12:15">
+      <c r="O19" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="20" spans="12:15">
+      <c r="L20" t="s">
+        <v>175</v>
+      </c>
+      <c r="O20" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="21" spans="12:15">
+      <c r="L21" t="s">
+        <v>176</v>
+      </c>
+      <c r="O21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="12:15">
+      <c r="L22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="12:15">
+      <c r="O23" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="24" spans="12:15">
+      <c r="L24" t="s">
+        <v>178</v>
+      </c>
+      <c r="O24" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25" spans="12:15">
+      <c r="L25" t="s">
+        <v>179</v>
+      </c>
+      <c r="O25" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26" spans="12:15">
+      <c r="L26" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="12:15">
+      <c r="O27" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="28" spans="12:15">
+      <c r="O28" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="12:15">
+      <c r="O29" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="31" spans="12:15">
+      <c r="O31" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="32" spans="12:15">
+      <c r="O32" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="33" spans="15:15">
+      <c r="O33" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="34" spans="15:15">
+      <c r="O34" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="15:15">
+      <c r="O35" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" spans="15:15">
+      <c r="O36" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="15:15">
+      <c r="O38" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="39" spans="15:15">
+      <c r="O39" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="40" spans="15:15">
+      <c r="O40" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="42" spans="15:15">
+      <c r="O42" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="43" spans="15:15">
+      <c r="O43" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="44" spans="15:15">
+      <c r="O44" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="45" spans="15:15">
+      <c r="O45" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="46" spans="15:15">
+      <c r="O46" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="47" spans="15:15">
+      <c r="O47" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="48" spans="15:15">
+      <c r="O48" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="49" spans="15:15">
+      <c r="O49" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="50" spans="15:15">
+      <c r="O50" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="51" spans="15:15">
+      <c r="O51" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="52" spans="15:15">
+      <c r="O52" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="53" spans="15:15">
+      <c r="O53" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="55" spans="15:15">
+      <c r="O55" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="56" spans="15:15">
+      <c r="O56" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="57" spans="15:15">
+      <c r="O57" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="58" spans="15:15">
+      <c r="O58" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="59" spans="15:15">
+      <c r="O59" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="60" spans="15:15">
+      <c r="O60" t="s">
+        <v>187</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>